--- a/05 - Cuotas de alumnos o socios.xlsx
+++ b/05 - Cuotas de alumnos o socios.xlsx
@@ -659,7 +659,7 @@
     <row r="12" ht="30" customHeight="1" s="21">
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Si te sirvió y querés colaborar, mi alias de Mercado Pago es igna.pelliza. Gracias.</t>
+          <t>¡Gracias! Si te sirvió y querés colaborar, mi alias de Mercado Pago es:  igna.pelliza</t>
         </is>
       </c>
     </row>
